--- a/education_forms/044_sea_level_changes_quiz--education_forms.xlsx
+++ b/education_forms/044_sea_level_changes_quiz--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'sea_level_rise':_'0-1_meters'}</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'Sea Level Rise': '0-1 meters'}</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'sea_level_rise':_'1-2_meters'}</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'Sea Level Rise': '1-2 meters'}</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'sea_level_rise':_'2-3_meters'}</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'Sea Level Rise': '2-3 meters'}</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'sea_level_rise':_'3-4_meters'}</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'Sea Level Rise': '3-4 meters'}</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'sea_level_rise':_'4-5_meters'}</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'Sea Level Rise': '4-5 meters'}</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'sea_level_rise':_'5-6_meters'}</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'Sea Level Rise': '5-6 meters'}</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'sea_level_rise':_'6-7_meters'}</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'Sea Level Rise': '6-7 meters'}</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'sea_level_rise':_'7-8_meters'}</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'Sea Level Rise': '7-8 meters'}</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -830,12 +830,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'sea_level_rise':_'more_than_8_meters'}</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'Sea Level Rise': 'More than 8 meters'}</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tide_stick</t>
+          <t>tide stick</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>satellite_imagery</t>
+          <t>satellite imagery</t>
         </is>
       </c>
     </row>
@@ -886,7 +886,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sea_level_gauge</t>
+          <t>sea level gauge</t>
         </is>
       </c>
     </row>
@@ -954,7 +954,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>saltwater_infiltration</t>
+          <t>saltwater infiltration</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>increased_salinity</t>
+          <t>increased salinity</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>increased_sedimentation</t>
+          <t>increased sedimentation</t>
         </is>
       </c>
     </row>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>loss_of_biodiversity</t>
+          <t>loss of biodiversity</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>loss_of_habitat</t>
+          <t>loss of habitat</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>build_flood_defenses</t>
+          <t>build flood defenses</t>
         </is>
       </c>
     </row>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>adapt_to_new_conditions</t>
+          <t>adapt to new conditions</t>
         </is>
       </c>
     </row>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>move_to_higher_ground</t>
+          <t>move to higher ground</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>sea_level_gates</t>
+          <t>sea level gates</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>restore_wetlands</t>
+          <t>restore wetlands</t>
         </is>
       </c>
     </row>
